--- a/Free rooms Jan26.xlsx
+++ b/Free rooms Jan26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ad.sast.org.uk\redirected-user-files\SHAStaffRedirectedFiles\Staff\Kate.BOTTERILL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AFD1A87-F5B0-4075-A86E-938D69DEF1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12221BA8-5F76-4054-8315-68742F53F7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{48014A31-AD53-4B67-A04D-85E73C5C3F8A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="80">
   <si>
     <t>Room</t>
   </si>
@@ -87,9 +87,6 @@
   </si>
   <si>
     <t>B2</t>
-  </si>
-  <si>
-    <t>B21</t>
   </si>
   <si>
     <t>B22</t>
@@ -373,21 +370,21 @@
   <dxfs count="2">
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -721,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE3051D-A1AC-464E-9652-A9E1F2B85FA2}">
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
@@ -733,154 +730,154 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AN1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AO1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AP1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AR1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AS1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AT1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AU1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AV1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AW1" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AX1" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AY1" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="AY1" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:51" x14ac:dyDescent="0.3">
@@ -2903,22 +2900,22 @@
         <v>16</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>3</v>
@@ -2927,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>2</v>
@@ -2939,25 +2936,25 @@
         <v>2</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O15" s="4" t="s">
         <v>2</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R15" s="4" t="s">
         <v>2</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U15" s="4" t="s">
         <v>2</v>
@@ -2969,16 +2966,16 @@
         <v>3</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z15" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AA15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB15" s="4" t="s">
         <v>3</v>
@@ -2987,13 +2984,13 @@
         <v>2</v>
       </c>
       <c r="AD15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG15" s="4" t="s">
         <v>3</v>
@@ -3002,10 +2999,10 @@
         <v>2</v>
       </c>
       <c r="AI15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK15" s="4" t="s">
         <v>3</v>
@@ -3014,13 +3011,13 @@
         <v>2</v>
       </c>
       <c r="AM15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN15" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AO15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP15" s="4" t="s">
         <v>2</v>
@@ -3035,7 +3032,7 @@
         <v>2</v>
       </c>
       <c r="AT15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU15" s="4" t="s">
         <v>3</v>
@@ -3044,10 +3041,10 @@
         <v>3</v>
       </c>
       <c r="AW15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX15" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY15" s="4" t="s">
         <v>3</v>
@@ -3058,7 +3055,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>3</v>
@@ -3079,7 +3076,7 @@
         <v>3</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>3</v>
@@ -3091,7 +3088,7 @@
         <v>3</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N16" s="4" t="s">
         <v>3</v>
@@ -3106,7 +3103,7 @@
         <v>3</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S16" s="4" t="s">
         <v>3</v>
@@ -3115,7 +3112,7 @@
         <v>3</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V16" s="4" t="s">
         <v>3</v>
@@ -3130,7 +3127,7 @@
         <v>3</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA16" s="4" t="s">
         <v>3</v>
@@ -3139,7 +3136,7 @@
         <v>3</v>
       </c>
       <c r="AC16" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD16" s="4" t="s">
         <v>3</v>
@@ -3154,7 +3151,7 @@
         <v>3</v>
       </c>
       <c r="AH16" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI16" s="4" t="s">
         <v>3</v>
@@ -3163,34 +3160,34 @@
         <v>3</v>
       </c>
       <c r="AK16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL16" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM16" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AN16" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO16" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AP16" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ16" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR16" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS16" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU16" s="4" t="s">
         <v>3</v>
@@ -3205,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AY16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:51" x14ac:dyDescent="0.3">
@@ -3216,16 +3213,16 @@
         <v>2</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>3</v>
@@ -3234,40 +3231,40 @@
         <v>3</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>2</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O17" s="4" t="s">
         <v>2</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R17" s="4" t="s">
         <v>3</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U17" s="4" t="s">
         <v>3</v>
@@ -3279,28 +3276,28 @@
         <v>3</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z17" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AA17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF17" s="4" t="s">
         <v>3</v>
@@ -3309,43 +3306,43 @@
         <v>3</v>
       </c>
       <c r="AH17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK17" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AL17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ17" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AR17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT17" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU17" s="4" t="s">
         <v>3</v>
@@ -3354,10 +3351,10 @@
         <v>3</v>
       </c>
       <c r="AW17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX17" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY17" s="4" t="s">
         <v>2</v>
@@ -3368,19 +3365,19 @@
         <v>19</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>3</v>
@@ -3389,16 +3386,16 @@
         <v>3</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M18" s="4" t="s">
         <v>2</v>
@@ -3407,22 +3404,22 @@
         <v>2</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R18" s="4" t="s">
         <v>3</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U18" s="4" t="s">
         <v>3</v>
@@ -3434,13 +3431,13 @@
         <v>3</v>
       </c>
       <c r="X18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="Z18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA18" s="4" t="s">
         <v>2</v>
@@ -3449,22 +3446,22 @@
         <v>2</v>
       </c>
       <c r="AC18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AE18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG18" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AH18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI18" s="4" t="s">
         <v>2</v>
@@ -3473,19 +3470,19 @@
         <v>2</v>
       </c>
       <c r="AK18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AM18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP18" s="4" t="s">
         <v>2</v>
@@ -3494,7 +3491,7 @@
         <v>3</v>
       </c>
       <c r="AR18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS18" s="4" t="s">
         <v>2</v>
@@ -3512,10 +3509,10 @@
         <v>2</v>
       </c>
       <c r="AX18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY18" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:51" x14ac:dyDescent="0.3">
@@ -3523,37 +3520,37 @@
         <v>20</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>3</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M19" s="4" t="s">
         <v>2</v>
@@ -3562,64 +3559,64 @@
         <v>2</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="Z19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AB19" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AE19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AG19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI19" s="4" t="s">
         <v>2</v>
@@ -3628,49 +3625,49 @@
         <v>2</v>
       </c>
       <c r="AK19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AM19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AQ19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AT19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AX19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:51" x14ac:dyDescent="0.3">
@@ -3678,154 +3675,154 @@
         <v>21</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="Y20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AA20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB20" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AF20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AH20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AN20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AP20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AV20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY20" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:51" x14ac:dyDescent="0.3">
@@ -3842,7 +3839,7 @@
         <v>3</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>3</v>
@@ -3851,7 +3848,7 @@
         <v>3</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>3</v>
@@ -3860,7 +3857,7 @@
         <v>3</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L21" s="4" t="s">
         <v>3</v>
@@ -3875,13 +3872,13 @@
         <v>3</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="4" t="s">
         <v>3</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S21" s="4" t="s">
         <v>3</v>
@@ -3899,34 +3896,34 @@
         <v>3</v>
       </c>
       <c r="X21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y21" s="4" t="s">
         <v>3</v>
       </c>
       <c r="Z21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA21" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AB21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC21" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AD21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF21" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AG21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH21" s="4" t="s">
         <v>3</v>
@@ -3935,7 +3932,7 @@
         <v>3</v>
       </c>
       <c r="AJ21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK21" s="4" t="s">
         <v>3</v>
@@ -3944,19 +3941,19 @@
         <v>3</v>
       </c>
       <c r="AM21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN21" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AO21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP21" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AQ21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR21" s="4" t="s">
         <v>3</v>
@@ -3968,7 +3965,7 @@
         <v>3</v>
       </c>
       <c r="AU21" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV21" s="4" t="s">
         <v>3</v>
@@ -3991,16 +3988,16 @@
         <v>3</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>3</v>
@@ -4012,7 +4009,7 @@
         <v>3</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>3</v>
@@ -4027,7 +4024,7 @@
         <v>3</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P22" s="4" t="s">
         <v>3</v>
@@ -4036,28 +4033,28 @@
         <v>3</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S22" s="4" t="s">
         <v>3</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z22" s="4" t="s">
         <v>3</v>
@@ -4066,16 +4063,16 @@
         <v>3</v>
       </c>
       <c r="AB22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC22" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AD22" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF22" s="4" t="s">
         <v>3</v>
@@ -4090,10 +4087,10 @@
         <v>3</v>
       </c>
       <c r="AJ22" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL22" s="4" t="s">
         <v>3</v>
@@ -4102,16 +4099,16 @@
         <v>3</v>
       </c>
       <c r="AN22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ22" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR22" s="4" t="s">
         <v>3</v>
@@ -4120,10 +4117,10 @@
         <v>3</v>
       </c>
       <c r="AT22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV22" s="4" t="s">
         <v>3</v>
@@ -4135,7 +4132,7 @@
         <v>3</v>
       </c>
       <c r="AY22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:51" x14ac:dyDescent="0.3">
@@ -4143,28 +4140,28 @@
         <v>24</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>2</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>2</v>
@@ -4173,19 +4170,19 @@
         <v>3</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O23" s="4" t="s">
         <v>2</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="4" t="s">
         <v>3</v>
@@ -4194,7 +4191,7 @@
         <v>3</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T23" s="4" t="s">
         <v>2</v>
@@ -4218,43 +4215,43 @@
         <v>3</v>
       </c>
       <c r="AA23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB23" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AC23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE23" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AF23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK23" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AL23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN23" s="4" t="s">
         <v>2</v>
@@ -4263,16 +4260,16 @@
         <v>2</v>
       </c>
       <c r="AP23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ23" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AR23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT23" s="4" t="s">
         <v>2</v>
@@ -4281,16 +4278,16 @@
         <v>2</v>
       </c>
       <c r="AV23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY23" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:51" x14ac:dyDescent="0.3">
@@ -4301,16 +4298,16 @@
         <v>2</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>2</v>
@@ -4319,28 +4316,28 @@
         <v>2</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>3</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>2</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="4" t="s">
         <v>3</v>
@@ -4349,46 +4346,46 @@
         <v>3</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z24" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AA24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD24" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AE24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG24" s="4" t="s">
         <v>2</v>
@@ -4397,7 +4394,7 @@
         <v>2</v>
       </c>
       <c r="AI24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ24" s="4" t="s">
         <v>2</v>
@@ -4409,10 +4406,10 @@
         <v>2</v>
       </c>
       <c r="AM24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO24" s="4" t="s">
         <v>2</v>
@@ -4424,25 +4421,25 @@
         <v>3</v>
       </c>
       <c r="AR24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS24" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AT24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU24" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AV24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX24" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY24" s="4" t="s">
         <v>3</v>
@@ -4456,7 +4453,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>3</v>
@@ -4465,13 +4462,13 @@
         <v>3</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>3</v>
@@ -4480,7 +4477,7 @@
         <v>3</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L25" s="4" t="s">
         <v>3</v>
@@ -4492,31 +4489,31 @@
         <v>3</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="4" t="s">
         <v>3</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T25" s="4" t="s">
         <v>3</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V25" s="4" t="s">
         <v>3</v>
       </c>
       <c r="W25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X25" s="4" t="s">
         <v>3</v>
@@ -4525,10 +4522,10 @@
         <v>3</v>
       </c>
       <c r="Z25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB25" s="4" t="s">
         <v>3</v>
@@ -4537,37 +4534,37 @@
         <v>3</v>
       </c>
       <c r="AD25" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF25" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AG25" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH25" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI25" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AJ25" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK25" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL25" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AM25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO25" s="4" t="s">
         <v>2</v>
@@ -4576,7 +4573,7 @@
         <v>3</v>
       </c>
       <c r="AQ25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR25" s="4" t="s">
         <v>3</v>
@@ -4585,22 +4582,22 @@
         <v>2</v>
       </c>
       <c r="AT25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU25" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW25" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AX25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY25" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:51" x14ac:dyDescent="0.3">
@@ -4614,10 +4611,10 @@
         <v>2</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>2</v>
@@ -4635,16 +4632,16 @@
         <v>3</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M26" s="4" t="s">
         <v>2</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O26" s="4" t="s">
         <v>2</v>
@@ -4656,34 +4653,34 @@
         <v>3</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T26" s="4" t="s">
         <v>3</v>
       </c>
       <c r="U26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V26" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W26" s="4" t="s">
         <v>2</v>
       </c>
       <c r="X26" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y26" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB26" s="4" t="s">
         <v>3</v>
@@ -4704,46 +4701,46 @@
         <v>3</v>
       </c>
       <c r="AH26" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI26" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AJ26" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK26" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AL26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP26" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AQ26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR26" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AS26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT26" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU26" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV26" s="4" t="s">
         <v>2</v>
@@ -4763,19 +4760,19 @@
         <v>28</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>3</v>
@@ -4793,19 +4790,19 @@
         <v>3</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M27" s="4" t="s">
         <v>2</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q27" s="4" t="s">
         <v>3</v>
@@ -4823,16 +4820,16 @@
         <v>3</v>
       </c>
       <c r="V27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W27" s="4" t="s">
         <v>2</v>
       </c>
       <c r="X27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z27" s="4" t="s">
         <v>3</v>
@@ -4847,10 +4844,10 @@
         <v>3</v>
       </c>
       <c r="AD27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF27" s="4" t="s">
         <v>3</v>
@@ -4859,13 +4856,13 @@
         <v>3</v>
       </c>
       <c r="AH27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AJ27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK27" s="4" t="s">
         <v>3</v>
@@ -4892,13 +4889,13 @@
         <v>3</v>
       </c>
       <c r="AS27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT27" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AU27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV27" s="4" t="s">
         <v>2</v>
@@ -4907,10 +4904,10 @@
         <v>3</v>
       </c>
       <c r="AX27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY27" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:51" x14ac:dyDescent="0.3">
@@ -4918,19 +4915,19 @@
         <v>29</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>3</v>
@@ -4948,19 +4945,19 @@
         <v>3</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M28" s="4" t="s">
         <v>2</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q28" s="4" t="s">
         <v>3</v>
@@ -4975,37 +4972,37 @@
         <v>3</v>
       </c>
       <c r="U28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W28" s="4" t="s">
         <v>2</v>
       </c>
       <c r="X28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD28" s="4" t="s">
         <v>2</v>
       </c>
       <c r="AE28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF28" s="4" t="s">
         <v>3</v>
@@ -5023,19 +5020,19 @@
         <v>3</v>
       </c>
       <c r="AK28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP28" s="4" t="s">
         <v>3</v>
@@ -5047,13 +5044,13 @@
         <v>3</v>
       </c>
       <c r="AS28" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT28" s="4" t="s">
         <v>3</v>
       </c>
       <c r="AU28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV28" s="4" t="s">
         <v>2</v>
@@ -5065,172 +5062,17 @@
         <v>3</v>
       </c>
       <c r="AY28" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="M29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="N29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="O29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="P29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="R29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="S29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="T29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="U29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="V29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="W29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="X29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AM29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AP29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AQ29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AR29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AS29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AT29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AU29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AV29" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AW29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AX29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AY29" s="4" t="s">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A29">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AY29">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Available">
+  <conditionalFormatting sqref="A1:AY28">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Available">
       <formula>NOT(ISERROR(SEARCH("Available",A1)))</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A28">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="60" fitToWidth="2" orientation="landscape" r:id="rId1"/>
